--- a/artfynd/A 10853-2025 artfynd.xlsx
+++ b/artfynd/A 10853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113245885</v>
+        <v>113245886</v>
       </c>
       <c r="B2" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667735</v>
+        <v>667764</v>
       </c>
       <c r="R2" t="n">
-        <v>6706016</v>
+        <v>6705979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,6 +771,1053 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>87140530</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Utmossarna 1,8 km VSV Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>667658</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6706059</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87140382</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Utmossarna 1,8 km VSV Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>667659</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6706084</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>87140427</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Utmossarna 1,8 km VSV Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>667659</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6706084</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>87140542</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Utmossarna 1,8 km VSV Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>667658</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6706059</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>87140363</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Utmossarna 1,8 km VSV Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>667659</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6706084</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113245882</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Göksnåre, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>667662</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6706017</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Axel Linder</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113245885</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Göksnåre, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>667735</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6706016</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Axel Linder</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Rätz, Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>87140470</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Utmossarna 1,8 km VSV Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>667659</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6706084</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>87140737</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Utmossarna 1,8 km VSV om Skaten, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>667652</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6706009</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-07-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 10853-2025 artfynd.xlsx
+++ b/artfynd/A 10853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245886</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87140530</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87140382</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87140427</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87140542</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1380,6 +1410,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87140363</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245882</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
           <t>CRZ0052 Göksnåre-Ängsskär Skoglig naturinventering 2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113245885</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1701,6 +1746,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87140470</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1820,8 +1870,25 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87140737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>